--- a/bug-reports/Suspition_Meter_Bug/Roadside_Research_Suspition_Meter_Bug.xlsx
+++ b/bug-reports/Suspition_Meter_Bug/Roadside_Research_Suspition_Meter_Bug.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\qa-portfolio\bug-reports\Suspition_Meter_Bug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4102430-8112-4B2A-8142-F632DE9C65E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13500BBC-1B71-4400-8C6C-31BE56F502EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,10 +93,10 @@
     <t>Low (Just a visual UI bug)</t>
   </si>
   <si>
-    <t>The "Current Sus Level" indicator cant be interacted with</t>
-  </si>
-  <si>
-    <t>The "Current Sus Level" indicator can be visually changed, but it does not affet gameplay</t>
+    <t>The "Current Sus Level" indicator can be visually changed, but it does not affect gameplay</t>
+  </si>
+  <si>
+    <t>The "Current Sus Level" indicator can't be interacted with</t>
   </si>
 </sst>
 </file>
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -341,9 +341,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -360,13 +357,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,7 +663,7 @@
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="3"/>
@@ -676,57 +673,57 @@
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="3"/>
@@ -736,7 +733,7 @@
       <c r="B11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="3"/>
@@ -746,7 +743,7 @@
       <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="3"/>
@@ -756,8 +753,8 @@
       <c r="B13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>21</v>
+      <c r="C13" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D13" s="3"/>
     </row>
@@ -766,8 +763,8 @@
       <c r="B14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>22</v>
+      <c r="C14" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -776,17 +773,17 @@
       <c r="B15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="3"/>
@@ -797,7 +794,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="B5:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
